--- a/baseline/data_processing_elements-NHANES13.xlsx
+++ b/baseline/data_processing_elements-NHANES13.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Computer\twey working files\ProPASS\NHANES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\twey\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{316440E4-2A94-41B1-89DE-1330A69FC813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56A3BD33-17F0-4861-9EF6-6F49DA17704D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3161BE6F-2E10-4AFE-B2DF-B65F0CC4B714}"/>
+    <workbookView xWindow="19090" yWindow="1840" windowWidth="19420" windowHeight="10300" xr2:uid="{3161BE6F-2E10-4AFE-B2DF-B65F0CC4B714}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
@@ -2095,38 +2095,12 @@
 . = Missing</t>
   </si>
   <si>
-    <t>SMD650;
-SMD641</t>
-  </si>
-  <si>
-    <t>Avg # cigarettes/day during past 30 days;
-# days smoked cigs during past 30 days</t>
-  </si>
-  <si>
     <t>During the past 30 days, on the days that {you/SP} smoked, about how many cigarettes did {you/s/he} smoke per day?;
 On how many of the past 30 days did {you/SP} smoke a cigarette?</t>
   </si>
   <si>
     <t>Both males and females 12 YEARS - 150 YEARS
 1 PACK EQUALS 20 CIGARETTES. IF LESS THAN 1 PER DAY, ENTER 1. IF 95 OR MORE PER DAY, ENTER 95. ENTER NUMBER (OF CIGARETTES) (PER DAY).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 to 80 = Range of Values
-1 = 1 cigarette or less
-95 = 95 cigarettes or more
-777 = Refused
-999 = Don't know
-. = Missing
-0 to 30 = Range of Values
-77 = Refused
-99 = Don't know
-. = Missing	</t>
-  </si>
-  <si>
-    <t xml:space="preserve">case_when(
-SMD650 %in% c(1:95) &amp; SMD641 %in% c(0:30) ~ round(SMD650*SMD641/(30/7), 2);
-ELSE ~ NA_real_)
-</t>
   </si>
   <si>
     <t>How much sleep do you get (hours)?</t>
@@ -2687,11 +2661,6 @@
   </si>
   <si>
     <t>MCQ160A</t>
-  </si>
-  <si>
-    <t>case_when(
-BMIWT != 4 &amp; ! is.na(BMIWT) ~ 2L; 
-ELSE ~ NA_integer_)</t>
   </si>
   <si>
     <t>DXDTOPF</t>
@@ -2885,15 +2854,6 @@
   </si>
   <si>
     <t>case_when(
-ALQ120Q %in% c(NA, 777, 999) | ALQ120U %in% c(NA, 7, 9) | ALQ130 %in%c(NA, 777, 999) ~ NA_real_;
-ALQ120Q == 0 ~ 0;
-ALQ120U == 1 ~ round( 14*ALQ130*ALQ120Q, 2);
-ALQ120U == 2 ~ round( 14*ALQ130*ALQ120Q*((12*7)/365.25), 2 );
-ALQ120U == 3 ~ round( 14*ALQ130*ALQ120Q * (7/365.25), 2);
-ELSE ~ NA_real_)</t>
-  </si>
-  <si>
-    <t>case_when(
 DR1_300 == 2 &amp; ! is.na(DR1TKCAL) &amp; DR1TKCAL &gt;0 ~ DR1TKCAL;
 DR2_300 == 2 &amp; ! is.na(DR2TKCAL) &amp; DR2TKCAL &gt;0 ~ DR2TKCAL;
 ELSE ~ NA_real_)</t>
@@ -3624,14 +3584,7 @@
     <t>Study-specific information is based on amount of food eaten yesterday, and only used if the participant responded that it was a usual amount. There are outlier values in the output.</t>
   </si>
   <si>
-    <t xml:space="preserve">The study-specific information was based on responses about alcohol use in the past 12 months. Mean grams of alcohol per standard drink in the United States (14g) was used for calculations. 
-</t>
-  </si>
-  <si>
     <t>Study participants were only considered as having smoked if they have smoked at least 100 cigarettes in their entire life.</t>
-  </si>
-  <si>
-    <t>The study-specific maximum was 95 cigarettes a day, and the minimum was  1 cigarette a day.</t>
   </si>
   <si>
     <t>The study-specific category "12 hours or more" was coded as 12.</t>
@@ -3690,6 +3643,61 @@
   <si>
     <t>Drug Code ; 
 Taken prescription medicine, past month</t>
+  </si>
+  <si>
+    <t>case_when(
+(!BMIWT %in% c(4)) &amp; (! is.na(BMIWT)) ~ 2L; 
+ELSE ~ NA_integer_)</t>
+  </si>
+  <si>
+    <t>Non-smokers (never smoked at least 100 cigarettes in life) were coded as 0. The study-specific maximum for Avg # cigarettes/day during past 30 days was 95 cigarettes a day, and the minimum was  1 cigarette a day.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">case_when(
+SMQ020 == 2 ~ 0L; 
+SMD650 %in% c(1:95) &amp; SMD641 %in% c(0:30) ~ round(SMD650*SMD641/(30/7), 2);
+ELSE ~ NA_real_)
+</t>
+  </si>
+  <si>
+    <t>SMQ020;
+SMD650;
+SMD641</t>
+  </si>
+  <si>
+    <t>Smoked at least 100 cigarettes in life;
+Avg # cigarettes/day during past 30 days;
+# days smoked cigs during past 30 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 = Yes;
+2 = No;
+7 = Refused;
+9 = Don't know;
+. = Missing	
+2 to 80 = Range of Values
+1 = 1 cigarette or less
+95 = 95 cigarettes or more
+777 = Refused
+999 = Don't know
+. = Missing
+0 to 30 = Range of Values
+77 = Refused
+99 = Don't know
+. = Missing	</t>
+  </si>
+  <si>
+    <t>case_when(
+ALQ120Q == 0 ~ 0;
+ALQ120Q %in% c(NA, 777, 999) | ALQ130 %in%c(NA, 777, 999) ~ NA_real_;
+ALQ120U == 1 ~ round( 14*ALQ130*ALQ120Q, 2);
+ALQ120U == 2 ~ round( 14*ALQ130*ALQ120Q*((12*7)/365.25), 2 );
+ALQ120U == 3 ~ round( 14*ALQ130*ALQ120Q * (7/365.25), 2);
+ELSE ~ NA_real_)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-drinkers were coded as 0. The study-specific information was based on responses about alcohol use in the past 12 months. Mean grams of alcohol per standard drink in the United States (14g) was used for calculations. 
+</t>
   </si>
 </sst>
 </file>
@@ -3786,10 +3794,10 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -4194,7 +4202,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>10</v>
@@ -4203,7 +4211,7 @@
         <v>11</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="O1" s="3" t="s">
         <v>12</v>
@@ -4224,10 +4232,10 @@
         <v>17</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="V1" s="4" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="W1" s="4" t="s">
         <v>18</v>
@@ -4261,16 +4269,16 @@
       </c>
     </row>
     <row r="2" spans="1:32" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C2" s="8" t="s">
+      <c r="B2" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="5" t="s">
         <v>147</v>
       </c>
       <c r="E2" s="5" t="s">
@@ -4289,7 +4297,7 @@
         <v>465</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="O2" s="5" t="s">
         <v>465</v>
@@ -4308,16 +4316,16 @@
       </c>
     </row>
     <row r="3" spans="1:32" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C3" s="8" t="s">
+      <c r="B3" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="5" t="s">
         <v>148</v>
       </c>
       <c r="E3" s="5" t="s">
@@ -4342,20 +4350,20 @@
         <v>470</v>
       </c>
       <c r="Y3" s="5" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
     </row>
     <row r="4" spans="1:32" s="5" customFormat="1" ht="165" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C4" s="8" t="s">
+      <c r="B4" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="5" t="s">
         <v>149</v>
       </c>
       <c r="E4" s="5" t="s">
@@ -4380,20 +4388,20 @@
         <v>470</v>
       </c>
       <c r="Y4" s="5" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
     </row>
     <row r="5" spans="1:32" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C5" s="8" t="s">
+      <c r="B5" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="5" t="s">
         <v>150</v>
       </c>
       <c r="E5" s="5" t="s">
@@ -4421,17 +4429,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:32" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:32" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C6" s="8" t="s">
+      <c r="B6" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="5" t="s">
         <v>151</v>
       </c>
       <c r="E6" s="5" t="s">
@@ -4450,7 +4458,7 @@
         <v>469</v>
       </c>
       <c r="U6" s="7" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="V6" s="5" t="s">
         <v>471</v>
@@ -4469,16 +4477,16 @@
       </c>
     </row>
     <row r="7" spans="1:32" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="B7" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="5" t="s">
         <v>152</v>
       </c>
       <c r="E7" s="5" t="s">
@@ -4497,7 +4505,7 @@
         <v>475</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="O7" s="5" t="s">
         <v>476</v>
@@ -4521,17 +4529,17 @@
         <v>480</v>
       </c>
     </row>
-    <row r="8" spans="1:32" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:32" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C8" s="8" t="s">
+      <c r="B8" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="5" t="s">
         <v>153</v>
       </c>
       <c r="E8" s="5" t="s">
@@ -4553,19 +4561,19 @@
         <v>482</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="O8" s="5" t="s">
         <v>483</v>
       </c>
       <c r="P8" s="5" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="R8" s="5" t="s">
         <v>484</v>
       </c>
       <c r="U8" s="7" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
       <c r="V8" s="5" t="s">
         <v>466</v>
@@ -4584,16 +4592,16 @@
       </c>
     </row>
     <row r="9" spans="1:32" s="5" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+      <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C9" s="8" t="s">
+      <c r="B9" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="5" t="s">
         <v>154</v>
       </c>
       <c r="E9" s="5" t="s">
@@ -4615,7 +4623,7 @@
         <v>488</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="O9" s="5" t="s">
         <v>489</v>
@@ -4627,7 +4635,7 @@
         <v>490</v>
       </c>
       <c r="U9" s="7" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="V9" s="5" t="s">
         <v>466</v>
@@ -4639,26 +4647,26 @@
         <v>492</v>
       </c>
       <c r="Y9" s="7" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="Z9" s="5" t="s">
         <v>493</v>
       </c>
       <c r="AB9" s="5" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
     </row>
     <row r="10" spans="1:32" s="5" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+      <c r="A10" s="5">
         <v>9</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C10" s="8" t="s">
+      <c r="B10" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="5" t="s">
         <v>155</v>
       </c>
       <c r="E10" s="5" t="s">
@@ -4680,7 +4688,7 @@
         <v>488</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="O10" s="5" t="s">
         <v>489</v>
@@ -4701,26 +4709,26 @@
         <v>492</v>
       </c>
       <c r="Y10" s="7" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="Z10" s="5" t="s">
         <v>493</v>
       </c>
       <c r="AB10" s="5" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
     </row>
     <row r="11" spans="1:32" s="5" customFormat="1" ht="276" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+      <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C11" s="8" t="s">
+      <c r="B11" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="5" t="s">
         <v>156</v>
       </c>
       <c r="E11" s="5" t="s">
@@ -4745,7 +4753,7 @@
         <v>495</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="O11" s="5" t="s">
         <v>496</v>
@@ -4770,16 +4778,16 @@
       </c>
     </row>
     <row r="12" spans="1:32" s="5" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
+      <c r="A12" s="5">
         <v>11</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C12" s="8" t="s">
+      <c r="B12" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="5" t="s">
         <v>157</v>
       </c>
       <c r="E12" s="5" t="s">
@@ -4804,7 +4812,7 @@
         <v>495</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="O12" s="5" t="s">
         <v>496</v>
@@ -4829,16 +4837,16 @@
       </c>
     </row>
     <row r="13" spans="1:32" s="5" customFormat="1" ht="120" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
+      <c r="A13" s="5">
         <v>12</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C13" s="8" t="s">
+      <c r="B13" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="5" t="s">
         <v>158</v>
       </c>
       <c r="E13" s="5" t="s">
@@ -4863,7 +4871,7 @@
         <v>495</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="O13" s="5" t="s">
         <v>496</v>
@@ -4888,16 +4896,16 @@
       </c>
     </row>
     <row r="14" spans="1:32" s="5" customFormat="1" ht="120" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
+      <c r="A14" s="5">
         <v>13</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C14" s="8" t="s">
+      <c r="B14" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E14" s="5" t="s">
@@ -4922,7 +4930,7 @@
         <v>495</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="O14" s="5" t="s">
         <v>496</v>
@@ -4947,16 +4955,16 @@
       </c>
     </row>
     <row r="15" spans="1:32" s="5" customFormat="1" ht="105" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
+      <c r="A15" s="5">
         <v>14</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C15" s="8" t="s">
+      <c r="B15" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="5" t="s">
         <v>160</v>
       </c>
       <c r="E15" s="5" t="s">
@@ -4981,7 +4989,7 @@
         <v>495</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="O15" s="5" t="s">
         <v>496</v>
@@ -5006,16 +5014,16 @@
       </c>
     </row>
     <row r="16" spans="1:32" s="5" customFormat="1" ht="105" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
+      <c r="A16" s="5">
         <v>15</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C16" s="8" t="s">
+      <c r="B16" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="5" t="s">
         <v>161</v>
       </c>
       <c r="E16" s="5" t="s">
@@ -5040,7 +5048,7 @@
         <v>495</v>
       </c>
       <c r="N16" s="5" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="O16" s="5" t="s">
         <v>496</v>
@@ -5065,16 +5073,16 @@
       </c>
     </row>
     <row r="17" spans="1:28" s="5" customFormat="1" ht="105" x14ac:dyDescent="0.25">
-      <c r="A17" s="8">
+      <c r="A17" s="5">
         <v>16</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C17" s="8" t="s">
+      <c r="B17" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="5" t="s">
         <v>162</v>
       </c>
       <c r="E17" s="5" t="s">
@@ -5099,7 +5107,7 @@
         <v>495</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="O17" s="5" t="s">
         <v>496</v>
@@ -5124,16 +5132,16 @@
       </c>
     </row>
     <row r="18" spans="1:28" s="5" customFormat="1" ht="105" x14ac:dyDescent="0.25">
-      <c r="A18" s="8">
+      <c r="A18" s="5">
         <v>17</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C18" s="8" t="s">
+      <c r="B18" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="5" t="s">
         <v>163</v>
       </c>
       <c r="E18" s="5" t="s">
@@ -5158,7 +5166,7 @@
         <v>495</v>
       </c>
       <c r="N18" s="5" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="O18" s="5" t="s">
         <v>496</v>
@@ -5182,17 +5190,17 @@
         <v>471</v>
       </c>
     </row>
-    <row r="19" spans="1:28" s="5" customFormat="1" ht="120" x14ac:dyDescent="0.25">
-      <c r="A19" s="8">
+    <row r="19" spans="1:28" s="5" customFormat="1" ht="135" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
         <v>18</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C19" s="8" t="s">
+      <c r="B19" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="5" t="s">
         <v>164</v>
       </c>
       <c r="E19" s="5" t="s">
@@ -5217,7 +5225,7 @@
         <v>495</v>
       </c>
       <c r="N19" s="5" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="O19" s="5" t="s">
         <v>496</v>
@@ -5229,7 +5237,7 @@
         <v>497</v>
       </c>
       <c r="U19" s="7" t="s">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="V19" s="5" t="s">
         <v>466</v>
@@ -5245,16 +5253,16 @@
       </c>
     </row>
     <row r="20" spans="1:28" s="5" customFormat="1" ht="180" x14ac:dyDescent="0.25">
-      <c r="A20" s="8">
+      <c r="A20" s="5">
         <v>19</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C20" s="8" t="s">
+      <c r="B20" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="5" t="s">
         <v>165</v>
       </c>
       <c r="E20" s="5" t="s">
@@ -5276,7 +5284,7 @@
         <v>505</v>
       </c>
       <c r="N20" s="5" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="O20" s="5" t="s">
         <v>506</v>
@@ -5288,7 +5296,7 @@
         <v>507</v>
       </c>
       <c r="U20" s="7" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c r="V20" s="5" t="s">
         <v>466</v>
@@ -5300,23 +5308,23 @@
         <v>479</v>
       </c>
       <c r="Y20" s="7" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="AB20" s="5" t="s">
-        <v>845</v>
+        <v>839</v>
       </c>
     </row>
     <row r="21" spans="1:28" s="5" customFormat="1" ht="315" x14ac:dyDescent="0.25">
-      <c r="A21" s="8">
+      <c r="A21" s="5">
         <v>20</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C21" s="8" t="s">
+      <c r="B21" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="5" t="s">
         <v>166</v>
       </c>
       <c r="E21" s="5" t="s">
@@ -5332,13 +5340,13 @@
         <v>426</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="M21" s="5" t="s">
         <v>511</v>
       </c>
       <c r="N21" s="5" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="O21" s="5" t="s">
         <v>512</v>
@@ -5353,7 +5361,7 @@
         <v>514</v>
       </c>
       <c r="U21" s="5" t="s">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="V21" s="5" t="s">
         <v>466</v>
@@ -5365,26 +5373,26 @@
         <v>492</v>
       </c>
       <c r="Y21" s="7" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="Z21" s="5" t="s">
         <v>509</v>
       </c>
       <c r="AB21" s="5" t="s">
-        <v>846</v>
+        <v>840</v>
       </c>
     </row>
     <row r="22" spans="1:28" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A22" s="8">
+      <c r="A22" s="5">
         <v>21</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C22" s="8" t="s">
+      <c r="B22" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="5" t="s">
         <v>167</v>
       </c>
       <c r="E22" s="5" t="s">
@@ -5397,13 +5405,13 @@
         <v>352</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="M22" s="5" t="s">
         <v>510</v>
       </c>
       <c r="N22" s="5" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="O22" s="5" t="s">
         <v>515</v>
@@ -5418,7 +5426,7 @@
         <v>517</v>
       </c>
       <c r="U22" s="7" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
       <c r="V22" s="5" t="s">
         <v>466</v>
@@ -5430,26 +5438,26 @@
         <v>492</v>
       </c>
       <c r="Y22" s="7" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="Z22" s="5" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="AB22" s="5" t="s">
-        <v>847</v>
+        <v>841</v>
       </c>
     </row>
     <row r="23" spans="1:28" s="5" customFormat="1" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8">
+      <c r="A23" s="5">
         <v>22</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C23" s="8" t="s">
+      <c r="B23" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="5" t="s">
         <v>168</v>
       </c>
       <c r="E23" s="5" t="s">
@@ -5459,22 +5467,22 @@
         <v>346</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="M23" s="5" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="N23" s="5" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="O23" s="5" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="S23" s="5" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="U23" s="7" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="V23" s="5" t="s">
         <v>466</v>
@@ -5486,23 +5494,23 @@
         <v>479</v>
       </c>
       <c r="Y23" s="5" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="Z23" s="5" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
     </row>
     <row r="24" spans="1:28" s="5" customFormat="1" ht="285" x14ac:dyDescent="0.25">
-      <c r="A24" s="8">
+      <c r="A24" s="5">
         <v>23</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C24" s="8" t="s">
+      <c r="B24" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="5" t="s">
         <v>169</v>
       </c>
       <c r="E24" s="5" t="s">
@@ -5524,7 +5532,7 @@
         <v>519</v>
       </c>
       <c r="N24" s="5" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="O24" s="5" t="s">
         <v>520</v>
@@ -5536,7 +5544,7 @@
         <v>521</v>
       </c>
       <c r="U24" s="7" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="V24" s="5" t="s">
         <v>466</v>
@@ -5548,26 +5556,26 @@
         <v>492</v>
       </c>
       <c r="Y24" s="7" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="Z24" s="5" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="AB24" s="5" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
     </row>
     <row r="25" spans="1:28" s="5" customFormat="1" ht="135" x14ac:dyDescent="0.25">
-      <c r="A25" s="8">
+      <c r="A25" s="5">
         <v>24</v>
       </c>
-      <c r="B25" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C25" s="8" t="s">
+      <c r="B25" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="5" t="s">
         <v>170</v>
       </c>
       <c r="E25" s="5" t="s">
@@ -5586,7 +5594,7 @@
         <v>523</v>
       </c>
       <c r="N25" s="5" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="O25" s="5" t="s">
         <v>523</v>
@@ -5610,23 +5618,23 @@
         <v>479</v>
       </c>
       <c r="Y25" s="7" t="s">
-        <v>815</v>
+        <v>809</v>
       </c>
       <c r="AB25" s="5" t="s">
-        <v>849</v>
+        <v>843</v>
       </c>
     </row>
     <row r="26" spans="1:28" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="8">
+      <c r="A26" s="5">
         <v>25</v>
       </c>
-      <c r="B26" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C26" s="8" t="s">
+      <c r="B26" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="5" t="s">
         <v>171</v>
       </c>
       <c r="E26" s="5" t="s">
@@ -5658,16 +5666,16 @@
       </c>
     </row>
     <row r="27" spans="1:28" s="5" customFormat="1" ht="120" x14ac:dyDescent="0.25">
-      <c r="A27" s="8">
+      <c r="A27" s="5">
         <v>26</v>
       </c>
-      <c r="B27" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C27" s="8" t="s">
+      <c r="B27" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="5" t="s">
         <v>172</v>
       </c>
       <c r="E27" s="5" t="s">
@@ -5683,13 +5691,13 @@
         <v>388</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="M27" s="5" t="s">
         <v>526</v>
       </c>
       <c r="N27" s="5" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="O27" s="5" t="s">
         <v>526</v>
@@ -5701,10 +5709,10 @@
         <v>513</v>
       </c>
       <c r="S27" s="5" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="U27" s="7" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="V27" s="5" t="s">
         <v>466</v>
@@ -5716,23 +5724,23 @@
         <v>492</v>
       </c>
       <c r="Y27" s="5" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="Z27" s="5" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
     </row>
     <row r="28" spans="1:28" s="5" customFormat="1" ht="163.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="8">
+      <c r="A28" s="5">
         <v>27</v>
       </c>
-      <c r="B28" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C28" s="8" t="s">
+      <c r="B28" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="5" t="s">
         <v>173</v>
       </c>
       <c r="E28" s="5" t="s">
@@ -5745,13 +5753,13 @@
         <v>430</v>
       </c>
       <c r="L28" s="5" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="M28" s="5" t="s">
         <v>526</v>
       </c>
       <c r="N28" s="5" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="O28" s="5" t="s">
         <v>526</v>
@@ -5763,7 +5771,7 @@
         <v>513</v>
       </c>
       <c r="S28" s="5" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="V28" s="5" t="s">
         <v>466</v>
@@ -5778,20 +5786,20 @@
         <v>528</v>
       </c>
       <c r="Z28" s="5" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
     </row>
     <row r="29" spans="1:28" s="5" customFormat="1" ht="135" x14ac:dyDescent="0.25">
-      <c r="A29" s="8">
+      <c r="A29" s="5">
         <v>28</v>
       </c>
-      <c r="B29" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C29" s="8" t="s">
+      <c r="B29" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" s="5" t="s">
         <v>174</v>
       </c>
       <c r="E29" s="5" t="s">
@@ -5807,13 +5815,13 @@
         <v>388</v>
       </c>
       <c r="L29" s="5" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="M29" s="5" t="s">
         <v>529</v>
       </c>
       <c r="N29" s="5" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="O29" s="5" t="s">
         <v>529</v>
@@ -5825,10 +5833,10 @@
         <v>513</v>
       </c>
       <c r="S29" s="5" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="U29" s="7" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="V29" s="5" t="s">
         <v>466</v>
@@ -5840,23 +5848,23 @@
         <v>492</v>
       </c>
       <c r="Y29" s="5" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="Z29" s="5" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
     </row>
     <row r="30" spans="1:28" s="5" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A30" s="8">
+      <c r="A30" s="5">
         <v>29</v>
       </c>
-      <c r="B30" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C30" s="8" t="s">
+      <c r="B30" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="D30" s="5" t="s">
         <v>175</v>
       </c>
       <c r="E30" s="5" t="s">
@@ -5869,13 +5877,13 @@
         <v>430</v>
       </c>
       <c r="L30" s="5" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="M30" s="5" t="s">
         <v>529</v>
       </c>
       <c r="N30" s="5" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="O30" s="5" t="s">
         <v>529</v>
@@ -5887,7 +5895,7 @@
         <v>513</v>
       </c>
       <c r="S30" s="5" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="V30" s="5" t="s">
         <v>466</v>
@@ -5899,23 +5907,23 @@
         <v>492</v>
       </c>
       <c r="Y30" s="5" t="s">
-        <v>694</v>
+        <v>883</v>
       </c>
       <c r="Z30" s="5" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
     </row>
     <row r="31" spans="1:28" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="8">
+      <c r="A31" s="5">
         <v>30</v>
       </c>
-      <c r="B31" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C31" s="8" t="s">
+      <c r="B31" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D31" s="5" t="s">
         <v>176</v>
       </c>
       <c r="E31" s="5" t="s">
@@ -5937,7 +5945,7 @@
         <v>532</v>
       </c>
       <c r="N31" s="5" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="O31" s="5" t="s">
         <v>532</v>
@@ -5962,16 +5970,16 @@
       </c>
     </row>
     <row r="32" spans="1:28" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A32" s="8">
+      <c r="A32" s="5">
         <v>31</v>
       </c>
-      <c r="B32" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C32" s="8" t="s">
+      <c r="B32" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D32" s="5" t="s">
         <v>177</v>
       </c>
       <c r="E32" s="5" t="s">
@@ -5987,13 +5995,13 @@
         <v>388</v>
       </c>
       <c r="L32" s="5" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="M32" s="5" t="s">
         <v>533</v>
       </c>
       <c r="N32" s="5" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="O32" s="5" t="s">
         <v>533</v>
@@ -6017,20 +6025,20 @@
         <v>485</v>
       </c>
       <c r="Z32" s="5" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
     </row>
     <row r="33" spans="1:28" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A33" s="8">
+      <c r="A33" s="5">
         <v>32</v>
       </c>
-      <c r="B33" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C33" s="8" t="s">
+      <c r="B33" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D33" s="5" t="s">
         <v>178</v>
       </c>
       <c r="E33" s="5" t="s">
@@ -6043,13 +6051,13 @@
         <v>430</v>
       </c>
       <c r="L33" s="5" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="M33" s="5" t="s">
         <v>533</v>
       </c>
       <c r="N33" s="5" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="O33" s="5" t="s">
         <v>533</v>
@@ -6074,16 +6082,16 @@
       </c>
     </row>
     <row r="34" spans="1:28" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="8">
+      <c r="A34" s="5">
         <v>33</v>
       </c>
-      <c r="B34" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C34" s="8" t="s">
+      <c r="B34" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="D34" s="5" t="s">
         <v>179</v>
       </c>
       <c r="E34" s="5" t="s">
@@ -6096,13 +6104,13 @@
         <v>356</v>
       </c>
       <c r="L34" s="5" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="M34" s="5" t="s">
         <v>535</v>
       </c>
       <c r="N34" s="5" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="O34" s="5" t="s">
         <v>535</v>
@@ -6114,10 +6122,10 @@
         <v>484</v>
       </c>
       <c r="S34" s="5" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="U34" s="7" t="s">
-        <v>884</v>
+        <v>876</v>
       </c>
       <c r="V34" s="5" t="s">
         <v>466</v>
@@ -6133,16 +6141,16 @@
       </c>
     </row>
     <row r="35" spans="1:28" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A35" s="8">
+      <c r="A35" s="5">
         <v>34</v>
       </c>
-      <c r="B35" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C35" s="8" t="s">
+      <c r="B35" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C35" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="5" t="s">
         <v>180</v>
       </c>
       <c r="E35" s="5" t="s">
@@ -6152,13 +6160,13 @@
         <v>346</v>
       </c>
       <c r="L35" s="5" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="M35" s="5" t="s">
         <v>535</v>
       </c>
       <c r="N35" s="5" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="O35" s="5" t="s">
         <v>535</v>
@@ -6170,7 +6178,7 @@
         <v>484</v>
       </c>
       <c r="S35" s="5" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="V35" s="5" t="s">
         <v>466</v>
@@ -6186,16 +6194,16 @@
       </c>
     </row>
     <row r="36" spans="1:28" s="5" customFormat="1" ht="315" x14ac:dyDescent="0.25">
-      <c r="A36" s="8">
+      <c r="A36" s="5">
         <v>35</v>
       </c>
-      <c r="B36" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C36" s="8" t="s">
+      <c r="B36" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C36" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="D36" s="5" t="s">
         <v>181</v>
       </c>
       <c r="E36" s="5" t="s">
@@ -6217,7 +6225,7 @@
         <v>539</v>
       </c>
       <c r="N36" s="5" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="O36" s="5" t="s">
         <v>539</v>
@@ -6229,10 +6237,10 @@
         <v>484</v>
       </c>
       <c r="S36" s="5" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="U36" s="7" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="V36" s="5" t="s">
         <v>466</v>
@@ -6244,26 +6252,26 @@
         <v>541</v>
       </c>
       <c r="Y36" s="7" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="Z36" s="5" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="AB36" s="5" t="s">
-        <v>850</v>
+        <v>844</v>
       </c>
     </row>
     <row r="37" spans="1:28" s="5" customFormat="1" ht="315" x14ac:dyDescent="0.25">
-      <c r="A37" s="8">
+      <c r="A37" s="5">
         <v>36</v>
       </c>
-      <c r="B37" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C37" s="8" t="s">
+      <c r="B37" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="D37" s="5" t="s">
         <v>182</v>
       </c>
       <c r="E37" s="5" t="s">
@@ -6285,7 +6293,7 @@
         <v>543</v>
       </c>
       <c r="N37" s="5" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="O37" s="5" t="s">
         <v>543</v>
@@ -6297,10 +6305,10 @@
         <v>484</v>
       </c>
       <c r="S37" s="5" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="U37" s="7" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="V37" s="5" t="s">
         <v>466</v>
@@ -6312,26 +6320,26 @@
         <v>541</v>
       </c>
       <c r="Y37" s="7" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="Z37" s="5" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="AB37" s="5" t="s">
-        <v>850</v>
+        <v>844</v>
       </c>
     </row>
     <row r="38" spans="1:28" s="5" customFormat="1" ht="105" x14ac:dyDescent="0.25">
-      <c r="A38" s="8">
+      <c r="A38" s="5">
         <v>37</v>
       </c>
-      <c r="B38" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C38" s="8" t="s">
+      <c r="B38" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C38" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D38" s="8" t="s">
+      <c r="D38" s="5" t="s">
         <v>183</v>
       </c>
       <c r="E38" s="5" t="s">
@@ -6347,13 +6355,13 @@
         <v>389</v>
       </c>
       <c r="L38" s="5" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="M38" s="5" t="s">
         <v>544</v>
       </c>
       <c r="N38" s="5" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="O38" s="5" t="s">
         <v>544</v>
@@ -6365,10 +6373,10 @@
         <v>484</v>
       </c>
       <c r="S38" s="5" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="U38" s="7" t="s">
-        <v>885</v>
+        <v>877</v>
       </c>
       <c r="V38" s="5" t="s">
         <v>466</v>
@@ -6380,23 +6388,23 @@
         <v>492</v>
       </c>
       <c r="Y38" s="5" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="Z38" s="5" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
     </row>
     <row r="39" spans="1:28" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A39" s="8">
+      <c r="A39" s="5">
         <v>38</v>
       </c>
-      <c r="B39" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C39" s="8" t="s">
+      <c r="B39" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D39" s="8" t="s">
+      <c r="D39" s="5" t="s">
         <v>184</v>
       </c>
       <c r="E39" s="5" t="s">
@@ -6428,16 +6436,16 @@
       </c>
     </row>
     <row r="40" spans="1:28" s="5" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A40" s="8">
+      <c r="A40" s="5">
         <v>39</v>
       </c>
-      <c r="B40" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C40" s="8" t="s">
+      <c r="B40" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D40" s="8" t="s">
+      <c r="D40" s="5" t="s">
         <v>185</v>
       </c>
       <c r="E40" s="5" t="s">
@@ -6450,13 +6458,13 @@
         <v>431</v>
       </c>
       <c r="L40" s="5" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="M40" s="5" t="s">
         <v>546</v>
       </c>
       <c r="N40" s="5" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="O40" s="5" t="s">
         <v>547</v>
@@ -6468,10 +6476,10 @@
         <v>484</v>
       </c>
       <c r="S40" s="5" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="U40" s="7" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="V40" s="5" t="s">
         <v>466</v>
@@ -6483,23 +6491,23 @@
         <v>492</v>
       </c>
       <c r="Y40" s="5" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="Z40" s="5" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="41" spans="1:28" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A41" s="8">
+      <c r="A41" s="5">
         <v>40</v>
       </c>
-      <c r="B41" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C41" s="8" t="s">
+      <c r="B41" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D41" s="8" t="s">
+      <c r="D41" s="5" t="s">
         <v>186</v>
       </c>
       <c r="E41" s="5" t="s">
@@ -6512,13 +6520,13 @@
         <v>360</v>
       </c>
       <c r="L41" s="5" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="M41" s="5" t="s">
         <v>550</v>
       </c>
       <c r="N41" s="5" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="O41" s="5" t="s">
         <v>550</v>
@@ -6530,7 +6538,7 @@
         <v>484</v>
       </c>
       <c r="S41" s="5" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="T41" s="5" t="s">
         <v>555</v>
@@ -6548,20 +6556,20 @@
         <v>485</v>
       </c>
       <c r="AB41" s="5" t="s">
-        <v>851</v>
+        <v>845</v>
       </c>
     </row>
     <row r="42" spans="1:28" s="5" customFormat="1" ht="90" x14ac:dyDescent="0.25">
-      <c r="A42" s="8">
+      <c r="A42" s="5">
         <v>41</v>
       </c>
-      <c r="B42" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C42" s="8" t="s">
+      <c r="B42" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D42" s="8" t="s">
+      <c r="D42" s="5" t="s">
         <v>187</v>
       </c>
       <c r="E42" s="5" t="s">
@@ -6574,13 +6582,13 @@
         <v>361</v>
       </c>
       <c r="L42" s="5" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="M42" s="5" t="s">
         <v>552</v>
       </c>
       <c r="N42" s="5" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="O42" s="5" t="s">
         <v>552</v>
@@ -6592,7 +6600,7 @@
         <v>484</v>
       </c>
       <c r="S42" s="5" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="T42" s="5" t="s">
         <v>356</v>
@@ -6607,26 +6615,26 @@
         <v>492</v>
       </c>
       <c r="Y42" s="7" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="Z42" s="5" t="s">
         <v>554</v>
       </c>
       <c r="AB42" s="5" t="s">
-        <v>852</v>
+        <v>846</v>
       </c>
     </row>
     <row r="43" spans="1:28" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A43" s="8">
+      <c r="A43" s="5">
         <v>42</v>
       </c>
-      <c r="B43" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C43" s="8" t="s">
+      <c r="B43" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C43" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D43" s="8" t="s">
+      <c r="D43" s="5" t="s">
         <v>188</v>
       </c>
       <c r="E43" s="5" t="s">
@@ -6639,25 +6647,25 @@
         <v>362</v>
       </c>
       <c r="L43" s="5" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="M43" s="5" t="s">
         <v>556</v>
       </c>
       <c r="N43" s="5" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="O43" s="5" t="s">
         <v>556</v>
       </c>
       <c r="P43" s="5" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="R43" s="5" t="s">
         <v>484</v>
       </c>
       <c r="S43" s="5" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="T43" s="5" t="s">
         <v>362</v>
@@ -6676,16 +6684,16 @@
       </c>
     </row>
     <row r="44" spans="1:28" s="5" customFormat="1" ht="90" x14ac:dyDescent="0.25">
-      <c r="A44" s="8">
+      <c r="A44" s="5">
         <v>43</v>
       </c>
-      <c r="B44" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C44" s="8" t="s">
+      <c r="B44" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D44" s="8" t="s">
+      <c r="D44" s="5" t="s">
         <v>189</v>
       </c>
       <c r="E44" s="5" t="s">
@@ -6698,25 +6706,25 @@
         <v>362</v>
       </c>
       <c r="L44" s="5" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="M44" s="5" t="s">
         <v>557</v>
       </c>
       <c r="N44" s="5" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="O44" s="5" t="s">
         <v>557</v>
       </c>
       <c r="P44" s="5" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="R44" s="5" t="s">
         <v>484</v>
       </c>
       <c r="S44" s="5" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="T44" s="5" t="s">
         <v>362</v>
@@ -6735,16 +6743,16 @@
       </c>
     </row>
     <row r="45" spans="1:28" s="5" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A45" s="8">
+      <c r="A45" s="5">
         <v>44</v>
       </c>
-      <c r="B45" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C45" s="8" t="s">
+      <c r="B45" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C45" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="D45" s="8" t="s">
+      <c r="D45" s="5" t="s">
         <v>190</v>
       </c>
       <c r="E45" s="5" t="s">
@@ -6772,20 +6780,20 @@
         <v>471</v>
       </c>
       <c r="Z45" s="5" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
     </row>
     <row r="46" spans="1:28" s="5" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A46" s="8">
+      <c r="A46" s="5">
         <v>45</v>
       </c>
-      <c r="B46" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C46" s="8" t="s">
+      <c r="B46" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C46" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D46" s="8" t="s">
+      <c r="D46" s="5" t="s">
         <v>191</v>
       </c>
       <c r="E46" s="5" t="s">
@@ -6801,19 +6809,19 @@
         <v>391</v>
       </c>
       <c r="L46" s="5" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="M46" s="5" t="s">
         <v>558</v>
       </c>
       <c r="N46" s="5" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="O46" s="5" t="s">
         <v>558</v>
       </c>
       <c r="P46" s="5" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="R46" s="5" t="s">
         <v>484</v>
@@ -6825,7 +6833,7 @@
         <v>362</v>
       </c>
       <c r="U46" s="7" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="V46" s="5" t="s">
         <v>466</v>
@@ -6840,20 +6848,20 @@
         <v>485</v>
       </c>
       <c r="Z46" s="5" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
     </row>
     <row r="47" spans="1:28" s="5" customFormat="1" ht="143.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="8">
+      <c r="A47" s="5">
         <v>46</v>
       </c>
-      <c r="B47" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C47" s="8" t="s">
+      <c r="B47" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C47" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="D47" s="8" t="s">
+      <c r="D47" s="5" t="s">
         <v>192</v>
       </c>
       <c r="E47" s="5" t="s">
@@ -6866,13 +6874,13 @@
         <v>362</v>
       </c>
       <c r="L47" s="5" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="M47" s="5" t="s">
         <v>560</v>
       </c>
       <c r="N47" s="5" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="O47" s="5" t="s">
         <v>560</v>
@@ -6884,7 +6892,7 @@
         <v>484</v>
       </c>
       <c r="S47" s="5" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="T47" s="5" t="s">
         <v>362</v>
@@ -6903,16 +6911,16 @@
       </c>
     </row>
     <row r="48" spans="1:28" s="5" customFormat="1" ht="73.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="8">
+      <c r="A48" s="5">
         <v>47</v>
       </c>
-      <c r="B48" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C48" s="8" t="s">
+      <c r="B48" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C48" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="D48" s="8" t="s">
+      <c r="D48" s="5" t="s">
         <v>193</v>
       </c>
       <c r="E48" s="5" t="s">
@@ -6941,16 +6949,16 @@
       </c>
     </row>
     <row r="49" spans="1:28" s="5" customFormat="1" ht="127.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="8">
+      <c r="A49" s="5">
         <v>48</v>
       </c>
-      <c r="B49" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C49" s="8" t="s">
+      <c r="B49" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C49" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D49" s="8" t="s">
+      <c r="D49" s="5" t="s">
         <v>194</v>
       </c>
       <c r="E49" s="5" t="s">
@@ -6982,16 +6990,16 @@
       </c>
     </row>
     <row r="50" spans="1:28" s="5" customFormat="1" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="8">
+      <c r="A50" s="5">
         <v>49</v>
       </c>
-      <c r="B50" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C50" s="8" t="s">
+      <c r="B50" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C50" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D50" s="8" t="s">
+      <c r="D50" s="5" t="s">
         <v>195</v>
       </c>
       <c r="E50" s="5" t="s">
@@ -7020,16 +7028,16 @@
       </c>
     </row>
     <row r="51" spans="1:28" s="5" customFormat="1" ht="90.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="8">
+      <c r="A51" s="5">
         <v>50</v>
       </c>
-      <c r="B51" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C51" s="8" t="s">
+      <c r="B51" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C51" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D51" s="8" t="s">
+      <c r="D51" s="5" t="s">
         <v>196</v>
       </c>
       <c r="E51" s="5" t="s">
@@ -7061,16 +7069,16 @@
       </c>
     </row>
     <row r="52" spans="1:28" s="5" customFormat="1" ht="81.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="8">
+      <c r="A52" s="5">
         <v>51</v>
       </c>
-      <c r="B52" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C52" s="8" t="s">
+      <c r="B52" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C52" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="D52" s="8" t="s">
+      <c r="D52" s="5" t="s">
         <v>197</v>
       </c>
       <c r="E52" s="5" t="s">
@@ -7102,16 +7110,16 @@
       </c>
     </row>
     <row r="53" spans="1:28" s="5" customFormat="1" ht="115.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="8">
+      <c r="A53" s="5">
         <v>52</v>
       </c>
-      <c r="B53" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C53" s="8" t="s">
+      <c r="B53" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C53" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="D53" s="8" t="s">
+      <c r="D53" s="5" t="s">
         <v>198</v>
       </c>
       <c r="E53" s="5" t="s">
@@ -7124,25 +7132,25 @@
         <v>365</v>
       </c>
       <c r="L53" s="5" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="M53" s="5" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="N53" s="5" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="O53" s="5" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="P53" s="5" t="s">
         <v>530</v>
       </c>
       <c r="S53" s="5" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="U53" s="7" t="s">
-        <v>869</v>
+        <v>863</v>
       </c>
       <c r="V53" s="5" t="s">
         <v>466</v>
@@ -7154,26 +7162,26 @@
         <v>492</v>
       </c>
       <c r="Y53" s="5" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="Z53" s="5" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="AB53" s="5" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="54" spans="1:28" s="5" customFormat="1" ht="103.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="8">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="54" spans="1:28" s="5" customFormat="1" ht="225" x14ac:dyDescent="0.25">
+      <c r="A54" s="5">
         <v>53</v>
       </c>
-      <c r="B54" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C54" s="8" t="s">
+      <c r="B54" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C54" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D54" s="8" t="s">
+      <c r="D54" s="5" t="s">
         <v>199</v>
       </c>
       <c r="E54" s="5" t="s">
@@ -7195,19 +7203,19 @@
         <v>562</v>
       </c>
       <c r="N54" s="5" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="O54" s="5" t="s">
         <v>563</v>
       </c>
       <c r="P54" s="5" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="S54" s="5" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="U54" s="7" t="s">
-        <v>870</v>
+        <v>890</v>
       </c>
       <c r="V54" s="5" t="s">
         <v>466</v>
@@ -7218,24 +7226,24 @@
       <c r="X54" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="Y54" s="5" t="s">
-        <v>735</v>
+      <c r="Y54" s="7" t="s">
+        <v>889</v>
       </c>
       <c r="Z54" s="5" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
     </row>
     <row r="55" spans="1:28" s="5" customFormat="1" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="8">
+      <c r="A55" s="5">
         <v>54</v>
       </c>
-      <c r="B55" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C55" s="8" t="s">
+      <c r="B55" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C55" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D55" s="8" t="s">
+      <c r="D55" s="5" t="s">
         <v>200</v>
       </c>
       <c r="E55" s="5" t="s">
@@ -7248,13 +7256,13 @@
         <v>433</v>
       </c>
       <c r="L55" s="5" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="M55" s="5" t="s">
         <v>567</v>
       </c>
       <c r="N55" s="5" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="O55" s="5" t="s">
         <v>568</v>
@@ -7272,26 +7280,26 @@
         <v>491</v>
       </c>
       <c r="X55" s="5" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="Y55" s="5" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="Z55" s="5" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
     </row>
     <row r="56" spans="1:28" s="5" customFormat="1" ht="180" x14ac:dyDescent="0.25">
-      <c r="A56" s="8">
+      <c r="A56" s="5">
         <v>55</v>
       </c>
-      <c r="B56" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C56" s="8" t="s">
+      <c r="B56" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C56" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D56" s="8" t="s">
+      <c r="D56" s="5" t="s">
         <v>201</v>
       </c>
       <c r="E56" s="5" t="s">
@@ -7307,13 +7315,13 @@
         <v>434</v>
       </c>
       <c r="L56" s="5" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="M56" s="5" t="s">
         <v>571</v>
       </c>
       <c r="N56" s="5" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="O56" s="5" t="s">
         <v>572</v>
@@ -7325,7 +7333,7 @@
         <v>574</v>
       </c>
       <c r="U56" s="7" t="s">
-        <v>871</v>
+        <v>864</v>
       </c>
       <c r="V56" s="5" t="s">
         <v>466</v>
@@ -7340,20 +7348,20 @@
         <v>575</v>
       </c>
       <c r="Z56" s="5" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
     </row>
     <row r="57" spans="1:28" s="5" customFormat="1" ht="105" x14ac:dyDescent="0.25">
-      <c r="A57" s="8">
+      <c r="A57" s="5">
         <v>56</v>
       </c>
-      <c r="B57" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C57" s="8" t="s">
+      <c r="B57" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C57" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="D57" s="8" t="s">
+      <c r="D57" s="5" t="s">
         <v>202</v>
       </c>
       <c r="E57" s="5" t="s">
@@ -7366,13 +7374,13 @@
         <v>435</v>
       </c>
       <c r="L57" s="5" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="M57" s="5" t="s">
         <v>569</v>
       </c>
       <c r="N57" s="5" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="O57" s="5" t="s">
         <v>570</v>
@@ -7384,7 +7392,7 @@
         <v>576</v>
       </c>
       <c r="U57" s="7" t="s">
-        <v>871</v>
+        <v>864</v>
       </c>
       <c r="V57" s="5" t="s">
         <v>466</v>
@@ -7399,17 +7407,17 @@
         <v>480</v>
       </c>
     </row>
-    <row r="58" spans="1:28" s="5" customFormat="1" ht="165" x14ac:dyDescent="0.25">
-      <c r="A58" s="8">
+    <row r="58" spans="1:28" s="5" customFormat="1" ht="255" x14ac:dyDescent="0.25">
+      <c r="A58" s="5">
         <v>57</v>
       </c>
-      <c r="B58" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C58" s="8" t="s">
+      <c r="B58" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C58" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="D58" s="8" t="s">
+      <c r="D58" s="5" t="s">
         <v>203</v>
       </c>
       <c r="E58" s="5" t="s">
@@ -7425,25 +7433,25 @@
         <v>397</v>
       </c>
       <c r="L58" s="5" t="s">
+        <v>886</v>
+      </c>
+      <c r="M58" s="5" t="s">
+        <v>887</v>
+      </c>
+      <c r="N58" s="5" t="s">
+        <v>777</v>
+      </c>
+      <c r="O58" s="5" t="s">
         <v>577</v>
       </c>
-      <c r="M58" s="5" t="s">
+      <c r="P58" s="5" t="s">
         <v>578</v>
       </c>
-      <c r="N58" s="5" t="s">
-        <v>783</v>
-      </c>
-      <c r="O58" s="5" t="s">
-        <v>579</v>
-      </c>
-      <c r="P58" s="5" t="s">
-        <v>580</v>
-      </c>
       <c r="S58" s="5" t="s">
-        <v>581</v>
+        <v>888</v>
       </c>
       <c r="U58" s="7" t="s">
-        <v>872</v>
+        <v>884</v>
       </c>
       <c r="V58" s="5" t="s">
         <v>466</v>
@@ -7454,24 +7462,24 @@
       <c r="X58" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="Y58" s="5" t="s">
-        <v>582</v>
+      <c r="Y58" s="7" t="s">
+        <v>885</v>
       </c>
       <c r="Z58" s="5" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
     </row>
     <row r="59" spans="1:28" s="5" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A59" s="8">
+      <c r="A59" s="5">
         <v>58</v>
       </c>
-      <c r="B59" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C59" s="8" t="s">
+      <c r="B59" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C59" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="D59" s="8" t="s">
+      <c r="D59" s="5" t="s">
         <v>204</v>
       </c>
       <c r="E59" s="5" t="s">
@@ -7484,22 +7492,22 @@
         <v>352</v>
       </c>
       <c r="L59" s="5" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="M59" s="5" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="N59" s="5" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="O59" s="5" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="S59" s="5" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="U59" s="7" t="s">
-        <v>873</v>
+        <v>865</v>
       </c>
       <c r="V59" s="5" t="s">
         <v>466</v>
@@ -7511,20 +7519,20 @@
         <v>492</v>
       </c>
       <c r="Y59" s="5" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="60" spans="1:28" s="5" customFormat="1" ht="165" x14ac:dyDescent="0.25">
-      <c r="A60" s="8">
+      <c r="A60" s="5">
         <v>59</v>
       </c>
-      <c r="B60" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C60" s="8" t="s">
+      <c r="B60" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C60" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="D60" s="8" t="s">
+      <c r="D60" s="5" t="s">
         <v>205</v>
       </c>
       <c r="E60" s="5" t="s">
@@ -7540,19 +7548,19 @@
         <v>436</v>
       </c>
       <c r="L60" s="5" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="M60" s="5" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="N60" s="5" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="O60" s="5" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="S60" s="5" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="V60" s="5" t="s">
         <v>466</v>
@@ -7564,20 +7572,20 @@
         <v>492</v>
       </c>
       <c r="Y60" s="5" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="61" spans="1:28" s="5" customFormat="1" ht="120" x14ac:dyDescent="0.25">
-      <c r="A61" s="8">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="61" spans="1:28" s="5" customFormat="1" ht="135" x14ac:dyDescent="0.25">
+      <c r="A61" s="5">
         <v>60</v>
       </c>
-      <c r="B61" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C61" s="8" t="s">
+      <c r="B61" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C61" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D61" s="8" t="s">
+      <c r="D61" s="5" t="s">
         <v>206</v>
       </c>
       <c r="E61" s="5" t="s">
@@ -7590,22 +7598,22 @@
         <v>437</v>
       </c>
       <c r="L61" s="5" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="M61" s="5" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="N61" s="5" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="O61" s="5" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="P61" s="5" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="S61" s="5" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="V61" s="5" t="s">
         <v>471</v>
@@ -7620,20 +7628,20 @@
         <v>471</v>
       </c>
       <c r="Z61" s="5" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
     </row>
     <row r="62" spans="1:28" s="5" customFormat="1" ht="150" x14ac:dyDescent="0.25">
-      <c r="A62" s="8">
+      <c r="A62" s="5">
         <v>61</v>
       </c>
-      <c r="B62" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C62" s="8" t="s">
+      <c r="B62" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C62" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="D62" s="8" t="s">
+      <c r="D62" s="5" t="s">
         <v>207</v>
       </c>
       <c r="E62" s="5" t="s">
@@ -7649,25 +7657,25 @@
         <v>438</v>
       </c>
       <c r="L62" s="5" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="M62" s="5" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="N62" s="5" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="O62" s="5" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="P62" s="5" t="s">
         <v>527</v>
       </c>
       <c r="S62" s="5" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="U62" s="7" t="s">
-        <v>874</v>
+        <v>866</v>
       </c>
       <c r="V62" s="5" t="s">
         <v>466</v>
@@ -7679,23 +7687,23 @@
         <v>479</v>
       </c>
       <c r="Y62" s="5" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="Z62" s="5" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="63" spans="1:28" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A63" s="8">
+      <c r="A63" s="5">
         <v>62</v>
       </c>
-      <c r="B63" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C63" s="8" t="s">
+      <c r="B63" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C63" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D63" s="8" t="s">
+      <c r="D63" s="5" t="s">
         <v>208</v>
       </c>
       <c r="E63" s="5" t="s">
@@ -7724,16 +7732,16 @@
       </c>
     </row>
     <row r="64" spans="1:28" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A64" s="8">
+      <c r="A64" s="5">
         <v>63</v>
       </c>
-      <c r="B64" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C64" s="8" t="s">
+      <c r="B64" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C64" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D64" s="8" t="s">
+      <c r="D64" s="5" t="s">
         <v>209</v>
       </c>
       <c r="E64" s="5" t="s">
@@ -7762,16 +7770,16 @@
       </c>
     </row>
     <row r="65" spans="1:28" s="5" customFormat="1" ht="180" x14ac:dyDescent="0.25">
-      <c r="A65" s="8">
+      <c r="A65" s="5">
         <v>64</v>
       </c>
-      <c r="B65" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C65" s="8" t="s">
+      <c r="B65" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C65" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D65" s="8" t="s">
+      <c r="D65" s="5" t="s">
         <v>210</v>
       </c>
       <c r="E65" s="5" t="s">
@@ -7784,25 +7792,25 @@
         <v>439</v>
       </c>
       <c r="L65" s="5" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="M65" s="5" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="N65" s="5" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="O65" s="5" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="P65" s="5" t="s">
         <v>527</v>
       </c>
       <c r="S65" s="5" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="U65" s="7" t="s">
-        <v>875</v>
+        <v>867</v>
       </c>
       <c r="V65" s="5" t="s">
         <v>466</v>
@@ -7817,20 +7825,20 @@
         <v>471</v>
       </c>
       <c r="Z65" s="5" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
     </row>
     <row r="66" spans="1:28" s="5" customFormat="1" ht="150" x14ac:dyDescent="0.25">
-      <c r="A66" s="8">
+      <c r="A66" s="5">
         <v>65</v>
       </c>
-      <c r="B66" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="D66" s="8" t="s">
+      <c r="B66" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>801</v>
+      </c>
+      <c r="D66" s="5" t="s">
         <v>211</v>
       </c>
       <c r="E66" s="5" t="s">
@@ -7846,25 +7854,25 @@
         <v>438</v>
       </c>
       <c r="L66" s="5" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="M66" s="5" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="N66" s="5" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="O66" s="5" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="P66" s="5" t="s">
         <v>527</v>
       </c>
       <c r="S66" s="5" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="U66" s="7" t="s">
-        <v>875</v>
+        <v>867</v>
       </c>
       <c r="V66" s="5" t="s">
         <v>471</v>
@@ -7880,16 +7888,16 @@
       </c>
     </row>
     <row r="67" spans="1:28" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A67" s="8">
+      <c r="A67" s="5">
         <v>66</v>
       </c>
-      <c r="B67" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C67" s="8" t="s">
+      <c r="B67" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C67" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="D67" s="8" t="s">
+      <c r="D67" s="5" t="s">
         <v>212</v>
       </c>
       <c r="E67" s="5" t="s">
@@ -7921,16 +7929,16 @@
       </c>
     </row>
     <row r="68" spans="1:28" s="5" customFormat="1" ht="195" x14ac:dyDescent="0.25">
-      <c r="A68" s="8">
+      <c r="A68" s="5">
         <v>67</v>
       </c>
-      <c r="B68" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>700</v>
-      </c>
-      <c r="D68" s="8" t="s">
+      <c r="B68" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>695</v>
+      </c>
+      <c r="D68" s="5" t="s">
         <v>213</v>
       </c>
       <c r="E68" s="5" t="s">
@@ -7946,54 +7954,54 @@
         <v>398</v>
       </c>
       <c r="L68" s="5" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="M68" s="5" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="N68" s="5" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="O68" s="5" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="P68" s="5" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="S68" s="5" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
       <c r="U68" s="7"/>
-      <c r="V68" s="9" t="s">
+      <c r="V68" s="8" t="s">
         <v>466</v>
       </c>
-      <c r="W68" s="9" t="s">
+      <c r="W68" s="8" t="s">
         <v>491</v>
       </c>
-      <c r="X68" s="9" t="s">
+      <c r="X68" s="8" t="s">
         <v>492</v>
       </c>
       <c r="Y68" s="7" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="Z68" s="5" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="AB68" s="5" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
     </row>
     <row r="69" spans="1:28" s="5" customFormat="1" ht="195" x14ac:dyDescent="0.25">
-      <c r="A69" s="8">
+      <c r="A69" s="5">
         <v>68</v>
       </c>
-      <c r="B69" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C69" s="8" t="s">
+      <c r="B69" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C69" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="D69" s="8" t="s">
+      <c r="D69" s="5" t="s">
         <v>214</v>
       </c>
       <c r="E69" s="5" t="s">
@@ -8006,57 +8014,57 @@
         <v>440</v>
       </c>
       <c r="L69" s="5" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="M69" s="5" t="s">
+        <v>597</v>
+      </c>
+      <c r="N69" s="5" t="s">
+        <v>779</v>
+      </c>
+      <c r="O69" s="5" t="s">
+        <v>598</v>
+      </c>
+      <c r="P69" s="5" t="s">
+        <v>599</v>
+      </c>
+      <c r="S69" s="5" t="s">
+        <v>600</v>
+      </c>
+      <c r="T69" s="5" t="s">
         <v>601</v>
       </c>
-      <c r="N69" s="5" t="s">
-        <v>785</v>
-      </c>
-      <c r="O69" s="5" t="s">
-        <v>602</v>
-      </c>
-      <c r="P69" s="5" t="s">
-        <v>603</v>
-      </c>
-      <c r="S69" s="5" t="s">
-        <v>604</v>
-      </c>
-      <c r="T69" s="5" t="s">
-        <v>605</v>
-      </c>
       <c r="U69" s="7"/>
-      <c r="V69" s="9" t="s">
+      <c r="V69" s="8" t="s">
         <v>466</v>
       </c>
-      <c r="W69" s="9" t="s">
+      <c r="W69" s="8" t="s">
         <v>491</v>
       </c>
-      <c r="X69" s="9" t="s">
+      <c r="X69" s="8" t="s">
         <v>492</v>
       </c>
       <c r="Y69" s="7" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="Z69" s="5" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="AB69" s="5" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
     </row>
     <row r="70" spans="1:28" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A70" s="8">
+      <c r="A70" s="5">
         <v>69</v>
       </c>
-      <c r="B70" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C70" s="8" t="s">
+      <c r="B70" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C70" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="D70" s="8" t="s">
+      <c r="D70" s="5" t="s">
         <v>215</v>
       </c>
       <c r="E70" s="5" t="s">
@@ -8085,16 +8093,16 @@
       </c>
     </row>
     <row r="71" spans="1:28" s="5" customFormat="1" ht="90" x14ac:dyDescent="0.25">
-      <c r="A71" s="8">
+      <c r="A71" s="5">
         <v>70</v>
       </c>
-      <c r="B71" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C71" s="8" t="s">
+      <c r="B71" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C71" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D71" s="8" t="s">
+      <c r="D71" s="5" t="s">
         <v>216</v>
       </c>
       <c r="E71" s="5" t="s">
@@ -8123,16 +8131,16 @@
       </c>
     </row>
     <row r="72" spans="1:28" s="5" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A72" s="8">
+      <c r="A72" s="5">
         <v>71</v>
       </c>
-      <c r="B72" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C72" s="8" t="s">
+      <c r="B72" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C72" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="D72" s="8" t="s">
+      <c r="D72" s="5" t="s">
         <v>217</v>
       </c>
       <c r="E72" s="5" t="s">
@@ -8148,28 +8156,28 @@
         <v>424</v>
       </c>
       <c r="L72" s="5" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
       <c r="M72" s="5" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="N72" s="5" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="O72" s="5" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="P72" s="5" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="R72" s="5" t="s">
         <v>477</v>
       </c>
       <c r="S72" s="5" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="U72" s="7" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="V72" s="5" t="s">
         <v>466</v>
@@ -8178,26 +8186,26 @@
         <v>491</v>
       </c>
       <c r="X72" s="5" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="Y72" s="5" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="Z72" s="5" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
     </row>
     <row r="73" spans="1:28" s="5" customFormat="1" ht="210" x14ac:dyDescent="0.25">
-      <c r="A73" s="8">
+      <c r="A73" s="5">
         <v>72</v>
       </c>
-      <c r="B73" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C73" s="8" t="s">
+      <c r="B73" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C73" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D73" s="8" t="s">
+      <c r="D73" s="5" t="s">
         <v>218</v>
       </c>
       <c r="E73" s="5" t="s">
@@ -8213,25 +8221,25 @@
         <v>424</v>
       </c>
       <c r="L73" s="5" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="M73" s="5" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="N73" s="5" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="O73" s="5" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="P73" s="5" t="s">
         <v>553</v>
       </c>
       <c r="S73" s="5" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="U73" s="7" t="s">
-        <v>876</v>
+        <v>868</v>
       </c>
       <c r="V73" s="5" t="s">
         <v>466</v>
@@ -8243,26 +8251,26 @@
         <v>492</v>
       </c>
       <c r="Y73" s="5" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="Z73" s="5" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="AB73" s="5" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
     </row>
     <row r="74" spans="1:28" s="5" customFormat="1" ht="285" x14ac:dyDescent="0.25">
-      <c r="A74" s="8">
+      <c r="A74" s="5">
         <v>73</v>
       </c>
-      <c r="B74" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C74" s="8" t="s">
+      <c r="B74" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C74" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="D74" s="8" t="s">
+      <c r="D74" s="5" t="s">
         <v>219</v>
       </c>
       <c r="E74" s="5" t="s">
@@ -8278,22 +8286,22 @@
         <v>424</v>
       </c>
       <c r="L74" s="5" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="M74" s="5" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="N74" s="5" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="O74" s="5" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="P74" s="5" t="s">
         <v>553</v>
       </c>
       <c r="S74" s="5" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="V74" s="5" t="s">
         <v>466</v>
@@ -8305,23 +8313,23 @@
         <v>492</v>
       </c>
       <c r="Y74" s="5" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="Z74" s="5" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
     </row>
     <row r="75" spans="1:28" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A75" s="8">
+      <c r="A75" s="5">
         <v>74</v>
       </c>
-      <c r="B75" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C75" s="8" t="s">
+      <c r="B75" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C75" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="D75" s="8" t="s">
+      <c r="D75" s="5" t="s">
         <v>220</v>
       </c>
       <c r="E75" s="5" t="s">
@@ -8350,16 +8358,16 @@
       </c>
     </row>
     <row r="76" spans="1:28" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A76" s="8">
+      <c r="A76" s="5">
         <v>75</v>
       </c>
-      <c r="B76" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C76" s="8" t="s">
+      <c r="B76" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C76" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D76" s="8" t="s">
+      <c r="D76" s="5" t="s">
         <v>221</v>
       </c>
       <c r="E76" s="5" t="s">
@@ -8388,16 +8396,16 @@
       </c>
     </row>
     <row r="77" spans="1:28" s="5" customFormat="1" ht="120" x14ac:dyDescent="0.25">
-      <c r="A77" s="8">
+      <c r="A77" s="5">
         <v>76</v>
       </c>
-      <c r="B77" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C77" s="8" t="s">
+      <c r="B77" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C77" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="D77" s="8" t="s">
+      <c r="D77" s="5" t="s">
         <v>222</v>
       </c>
       <c r="E77" s="5" t="s">
@@ -8410,22 +8418,22 @@
         <v>443</v>
       </c>
       <c r="L77" s="5" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="M77" s="5" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="N77" s="5" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="O77" s="5" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="P77" s="5" t="s">
         <v>553</v>
       </c>
       <c r="S77" s="5" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="V77" s="5" t="s">
         <v>466</v>
@@ -8437,20 +8445,20 @@
         <v>479</v>
       </c>
       <c r="Y77" s="5" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
     </row>
     <row r="78" spans="1:28" s="5" customFormat="1" ht="360" x14ac:dyDescent="0.25">
-      <c r="A78" s="8">
+      <c r="A78" s="5">
         <v>77</v>
       </c>
-      <c r="B78" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C78" s="8" t="s">
+      <c r="B78" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C78" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="D78" s="8" t="s">
+      <c r="D78" s="5" t="s">
         <v>223</v>
       </c>
       <c r="E78" s="5" t="s">
@@ -8466,28 +8474,28 @@
         <v>444</v>
       </c>
       <c r="L78" s="5" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="M78" s="5" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="N78" s="5" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="O78" s="5" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="P78" s="5" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="R78" s="5" t="s">
         <v>477</v>
       </c>
       <c r="S78" s="5" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="U78" s="7" t="s">
-        <v>877</v>
+        <v>869</v>
       </c>
       <c r="V78" s="5" t="s">
         <v>466</v>
@@ -8499,23 +8507,23 @@
         <v>492</v>
       </c>
       <c r="Y78" s="5" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="AB78" s="5" t="s">
-        <v>887</v>
+        <v>879</v>
       </c>
     </row>
     <row r="79" spans="1:28" s="5" customFormat="1" ht="255" x14ac:dyDescent="0.25">
-      <c r="A79" s="8">
+      <c r="A79" s="5">
         <v>78</v>
       </c>
-      <c r="B79" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C79" s="8" t="s">
+      <c r="B79" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C79" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="D79" s="8" t="s">
+      <c r="D79" s="5" t="s">
         <v>224</v>
       </c>
       <c r="E79" s="5" t="s">
@@ -8534,16 +8542,16 @@
         <v>444</v>
       </c>
       <c r="L79" s="5" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="M79" s="5" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="N79" s="5" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="O79" s="5" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="P79" s="5" t="s">
         <v>524</v>
@@ -8552,10 +8560,10 @@
         <v>477</v>
       </c>
       <c r="S79" s="5" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="U79" s="7" t="s">
-        <v>878</v>
+        <v>870</v>
       </c>
       <c r="V79" s="5" t="s">
         <v>466</v>
@@ -8567,26 +8575,26 @@
         <v>479</v>
       </c>
       <c r="Y79" s="5" t="s">
-        <v>795</v>
+        <v>789</v>
       </c>
       <c r="Z79" s="5" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
       <c r="AB79" s="5" t="s">
-        <v>888</v>
+        <v>880</v>
       </c>
     </row>
     <row r="80" spans="1:28" s="5" customFormat="1" ht="255" x14ac:dyDescent="0.25">
-      <c r="A80" s="8">
+      <c r="A80" s="5">
         <v>79</v>
       </c>
-      <c r="B80" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C80" s="8" t="s">
+      <c r="B80" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C80" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="D80" s="8" t="s">
+      <c r="D80" s="5" t="s">
         <v>225</v>
       </c>
       <c r="E80" s="5" t="s">
@@ -8605,16 +8613,16 @@
         <v>444</v>
       </c>
       <c r="L80" s="5" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="M80" s="5" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="N80" s="5" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="O80" s="5" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="P80" s="5" t="s">
         <v>524</v>
@@ -8623,35 +8631,35 @@
         <v>477</v>
       </c>
       <c r="S80" s="5" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="U80" s="7" t="s">
-        <v>879</v>
-      </c>
-      <c r="V80" s="5" t="s">
+        <v>871</v>
+      </c>
+      <c r="V80" s="9" t="s">
         <v>466</v>
       </c>
-      <c r="W80" s="5" t="s">
+      <c r="W80" s="9" t="s">
         <v>491</v>
       </c>
-      <c r="X80" s="5" t="s">
+      <c r="X80" s="9" t="s">
         <v>479</v>
       </c>
-      <c r="Y80" s="5" t="s">
-        <v>795</v>
+      <c r="Y80" s="8" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="81" spans="1:28" s="5" customFormat="1" ht="255" x14ac:dyDescent="0.25">
-      <c r="A81" s="8">
+      <c r="A81" s="5">
         <v>80</v>
       </c>
-      <c r="B81" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C81" s="8" t="s">
+      <c r="B81" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C81" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D81" s="8" t="s">
+      <c r="D81" s="5" t="s">
         <v>226</v>
       </c>
       <c r="E81" s="5" t="s">
@@ -8670,16 +8678,16 @@
         <v>444</v>
       </c>
       <c r="L81" s="5" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="M81" s="5" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="N81" s="5" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="O81" s="5" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="P81" s="5" t="s">
         <v>524</v>
@@ -8688,7 +8696,7 @@
         <v>477</v>
       </c>
       <c r="S81" s="5" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="V81" s="5" t="s">
         <v>466</v>
@@ -8700,20 +8708,20 @@
         <v>479</v>
       </c>
       <c r="Y81" s="5" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
     </row>
     <row r="82" spans="1:28" s="5" customFormat="1" ht="255" x14ac:dyDescent="0.25">
-      <c r="A82" s="8">
+      <c r="A82" s="5">
         <v>81</v>
       </c>
-      <c r="B82" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C82" s="8" t="s">
+      <c r="B82" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C82" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="D82" s="8" t="s">
+      <c r="D82" s="5" t="s">
         <v>227</v>
       </c>
       <c r="E82" s="5" t="s">
@@ -8732,16 +8740,16 @@
         <v>444</v>
       </c>
       <c r="L82" s="5" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="M82" s="5" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="N82" s="5" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="O82" s="5" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="P82" s="5" t="s">
         <v>524</v>
@@ -8750,7 +8758,7 @@
         <v>477</v>
       </c>
       <c r="S82" s="5" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="V82" s="5" t="s">
         <v>466</v>
@@ -8762,20 +8770,20 @@
         <v>479</v>
       </c>
       <c r="Y82" s="5" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
     </row>
     <row r="83" spans="1:28" s="5" customFormat="1" ht="255" x14ac:dyDescent="0.25">
-      <c r="A83" s="8">
+      <c r="A83" s="5">
         <v>82</v>
       </c>
-      <c r="B83" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C83" s="8" t="s">
+      <c r="B83" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C83" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D83" s="8" t="s">
+      <c r="D83" s="5" t="s">
         <v>228</v>
       </c>
       <c r="E83" s="5" t="s">
@@ -8794,16 +8802,16 @@
         <v>444</v>
       </c>
       <c r="L83" s="5" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="M83" s="5" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="N83" s="5" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="O83" s="5" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="P83" s="5" t="s">
         <v>524</v>
@@ -8812,7 +8820,7 @@
         <v>477</v>
       </c>
       <c r="S83" s="5" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="V83" s="5" t="s">
         <v>466</v>
@@ -8824,20 +8832,20 @@
         <v>479</v>
       </c>
       <c r="Y83" s="5" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
     </row>
     <row r="84" spans="1:28" s="5" customFormat="1" ht="255" x14ac:dyDescent="0.25">
-      <c r="A84" s="8">
+      <c r="A84" s="5">
         <v>83</v>
       </c>
-      <c r="B84" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C84" s="8" t="s">
+      <c r="B84" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C84" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="D84" s="8" t="s">
+      <c r="D84" s="5" t="s">
         <v>229</v>
       </c>
       <c r="E84" s="5" t="s">
@@ -8872,16 +8880,16 @@
       </c>
     </row>
     <row r="85" spans="1:28" s="5" customFormat="1" ht="315" x14ac:dyDescent="0.25">
-      <c r="A85" s="8">
+      <c r="A85" s="5">
         <v>84</v>
       </c>
-      <c r="B85" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C85" s="8" t="s">
+      <c r="B85" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C85" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="D85" s="8" t="s">
+      <c r="D85" s="5" t="s">
         <v>230</v>
       </c>
       <c r="E85" s="5" t="s">
@@ -8900,25 +8908,25 @@
         <v>444</v>
       </c>
       <c r="L85" s="5" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="M85" s="5" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="N85" s="5" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="O85" s="5" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="P85" s="5" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="R85" s="5" t="s">
         <v>477</v>
       </c>
       <c r="S85" s="5" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="V85" s="5" t="s">
         <v>466</v>
@@ -8930,20 +8938,20 @@
         <v>479</v>
       </c>
       <c r="Y85" s="5" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
     </row>
     <row r="86" spans="1:28" s="5" customFormat="1" ht="240" x14ac:dyDescent="0.25">
-      <c r="A86" s="8">
+      <c r="A86" s="5">
         <v>85</v>
       </c>
-      <c r="B86" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C86" s="8" t="s">
+      <c r="B86" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C86" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D86" s="8" t="s">
+      <c r="D86" s="5" t="s">
         <v>231</v>
       </c>
       <c r="E86" s="5" t="s">
@@ -8962,28 +8970,28 @@
         <v>444</v>
       </c>
       <c r="L86" s="5" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="M86" s="5" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="N86" s="5" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="O86" s="5" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="P86" s="5" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="R86" s="5" t="s">
         <v>477</v>
       </c>
       <c r="S86" s="5" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="U86" s="7" t="s">
-        <v>880</v>
+        <v>872</v>
       </c>
       <c r="V86" s="5" t="s">
         <v>466</v>
@@ -8995,23 +9003,23 @@
         <v>492</v>
       </c>
       <c r="Y86" s="5" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
       <c r="Z86" s="5" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
     </row>
     <row r="87" spans="1:28" s="5" customFormat="1" ht="255" x14ac:dyDescent="0.25">
-      <c r="A87" s="8">
+      <c r="A87" s="5">
         <v>86</v>
       </c>
-      <c r="B87" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C87" s="8" t="s">
+      <c r="B87" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C87" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D87" s="8" t="s">
+      <c r="D87" s="5" t="s">
         <v>232</v>
       </c>
       <c r="E87" s="5" t="s">
@@ -9030,16 +9038,16 @@
         <v>444</v>
       </c>
       <c r="L87" s="5" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="M87" s="5" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="N87" s="5" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="O87" s="5" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="P87" s="5" t="s">
         <v>524</v>
@@ -9048,10 +9056,10 @@
         <v>477</v>
       </c>
       <c r="S87" s="5" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="U87" s="7" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
       <c r="V87" s="5" t="s">
         <v>466</v>
@@ -9063,20 +9071,20 @@
         <v>479</v>
       </c>
       <c r="Y87" s="5" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
     </row>
     <row r="88" spans="1:28" s="5" customFormat="1" ht="255" x14ac:dyDescent="0.25">
-      <c r="A88" s="8">
+      <c r="A88" s="5">
         <v>87</v>
       </c>
-      <c r="B88" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C88" s="8" t="s">
+      <c r="B88" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C88" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="D88" s="8" t="s">
+      <c r="D88" s="5" t="s">
         <v>233</v>
       </c>
       <c r="E88" s="5" t="s">
@@ -9095,16 +9103,16 @@
         <v>444</v>
       </c>
       <c r="L88" s="5" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="M88" s="5" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="N88" s="5" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="O88" s="5" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="P88" s="5" t="s">
         <v>551</v>
@@ -9113,7 +9121,7 @@
         <v>477</v>
       </c>
       <c r="S88" s="5" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="V88" s="5" t="s">
         <v>466</v>
@@ -9125,20 +9133,20 @@
         <v>479</v>
       </c>
       <c r="Y88" s="5" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
     </row>
     <row r="89" spans="1:28" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A89" s="8">
+      <c r="A89" s="5">
         <v>88</v>
       </c>
-      <c r="B89" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C89" s="8" t="s">
+      <c r="B89" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C89" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="D89" s="8" t="s">
+      <c r="D89" s="5" t="s">
         <v>234</v>
       </c>
       <c r="E89" s="5" t="s">
@@ -9167,16 +9175,16 @@
       </c>
     </row>
     <row r="90" spans="1:28" s="5" customFormat="1" ht="180" x14ac:dyDescent="0.25">
-      <c r="A90" s="8">
+      <c r="A90" s="5">
         <v>89</v>
       </c>
-      <c r="B90" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C90" s="8" t="s">
+      <c r="B90" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C90" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="D90" s="8" t="s">
+      <c r="D90" s="5" t="s">
         <v>235</v>
       </c>
       <c r="E90" s="5" t="s">
@@ -9192,16 +9200,16 @@
         <v>444</v>
       </c>
       <c r="L90" s="5" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="M90" s="5" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="N90" s="5" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="O90" s="5" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="P90" s="5" t="s">
         <v>524</v>
@@ -9210,7 +9218,7 @@
         <v>477</v>
       </c>
       <c r="S90" s="5" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="V90" s="5" t="s">
         <v>466</v>
@@ -9222,20 +9230,20 @@
         <v>479</v>
       </c>
       <c r="Y90" s="5" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
     </row>
     <row r="91" spans="1:28" s="5" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A91" s="8">
+      <c r="A91" s="5">
         <v>90</v>
       </c>
-      <c r="B91" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C91" s="8" t="s">
+      <c r="B91" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C91" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D91" s="8" t="s">
+      <c r="D91" s="5" t="s">
         <v>236</v>
       </c>
       <c r="E91" s="5" t="s">
@@ -9251,25 +9259,25 @@
         <v>444</v>
       </c>
       <c r="L91" s="5" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="M91" s="5" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="N91" s="5" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="O91" s="5" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="P91" s="5" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="R91" s="5" t="s">
         <v>477</v>
       </c>
       <c r="S91" s="5" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="V91" s="5" t="s">
         <v>466</v>
@@ -9281,26 +9289,26 @@
         <v>492</v>
       </c>
       <c r="Y91" s="7" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="Z91" s="5" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="AB91" s="5" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
     </row>
     <row r="92" spans="1:28" s="5" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A92" s="8">
+      <c r="A92" s="5">
         <v>91</v>
       </c>
-      <c r="B92" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C92" s="8" t="s">
+      <c r="B92" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C92" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D92" s="8" t="s">
+      <c r="D92" s="5" t="s">
         <v>237</v>
       </c>
       <c r="E92" s="5" t="s">
@@ -9316,25 +9324,25 @@
         <v>444</v>
       </c>
       <c r="L92" s="5" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="M92" s="5" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="N92" s="5" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="O92" s="5" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="P92" s="5" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="R92" s="5" t="s">
         <v>477</v>
       </c>
       <c r="S92" s="5" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="V92" s="5" t="s">
         <v>466</v>
@@ -9346,26 +9354,26 @@
         <v>492</v>
       </c>
       <c r="Y92" s="7" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="Z92" s="5" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="AB92" s="5" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
     </row>
     <row r="93" spans="1:28" s="5" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A93" s="8">
+      <c r="A93" s="5">
         <v>92</v>
       </c>
-      <c r="B93" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C93" s="8" t="s">
+      <c r="B93" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C93" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D93" s="8" t="s">
+      <c r="D93" s="5" t="s">
         <v>238</v>
       </c>
       <c r="E93" s="5" t="s">
@@ -9381,25 +9389,25 @@
         <v>444</v>
       </c>
       <c r="L93" s="5" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="M93" s="5" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="N93" s="5" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="O93" s="5" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="P93" s="5" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="R93" s="5" t="s">
         <v>477</v>
       </c>
       <c r="S93" s="5" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="V93" s="5" t="s">
         <v>466</v>
@@ -9411,26 +9419,26 @@
         <v>492</v>
       </c>
       <c r="Y93" s="7" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="Z93" s="5" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="AB93" s="5" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
     </row>
     <row r="94" spans="1:28" s="5" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A94" s="8">
+      <c r="A94" s="5">
         <v>93</v>
       </c>
-      <c r="B94" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C94" s="8" t="s">
+      <c r="B94" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C94" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="D94" s="8" t="s">
+      <c r="D94" s="5" t="s">
         <v>239</v>
       </c>
       <c r="E94" s="5" t="s">
@@ -9446,25 +9454,25 @@
         <v>444</v>
       </c>
       <c r="L94" s="5" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="M94" s="5" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="N94" s="5" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="O94" s="5" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="P94" s="5" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="R94" s="5" t="s">
         <v>477</v>
       </c>
       <c r="S94" s="5" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="V94" s="5" t="s">
         <v>466</v>
@@ -9476,26 +9484,26 @@
         <v>492</v>
       </c>
       <c r="Y94" s="7" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="Z94" s="5" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="AB94" s="5" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
     </row>
     <row r="95" spans="1:28" s="5" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A95" s="8">
+      <c r="A95" s="5">
         <v>94</v>
       </c>
-      <c r="B95" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C95" s="8" t="s">
+      <c r="B95" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C95" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D95" s="8" t="s">
+      <c r="D95" s="5" t="s">
         <v>240</v>
       </c>
       <c r="E95" s="5" t="s">
@@ -9511,25 +9519,25 @@
         <v>444</v>
       </c>
       <c r="L95" s="5" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="M95" s="5" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="N95" s="5" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="O95" s="5" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="P95" s="5" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="R95" s="5" t="s">
         <v>477</v>
       </c>
       <c r="S95" s="5" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="V95" s="5" t="s">
         <v>466</v>
@@ -9541,26 +9549,26 @@
         <v>492</v>
       </c>
       <c r="Y95" s="7" t="s">
-        <v>825</v>
+        <v>819</v>
       </c>
       <c r="Z95" s="5" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="AB95" s="5" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
     </row>
     <row r="96" spans="1:28" s="5" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A96" s="8">
+      <c r="A96" s="5">
         <v>95</v>
       </c>
-      <c r="B96" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C96" s="8" t="s">
+      <c r="B96" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C96" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="D96" s="8" t="s">
+      <c r="D96" s="5" t="s">
         <v>241</v>
       </c>
       <c r="E96" s="5" t="s">
@@ -9576,25 +9584,25 @@
         <v>444</v>
       </c>
       <c r="L96" s="5" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="M96" s="5" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="N96" s="5" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="O96" s="5" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="P96" s="5" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="R96" s="5" t="s">
         <v>477</v>
       </c>
       <c r="S96" s="5" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="V96" s="5" t="s">
         <v>466</v>
@@ -9606,26 +9614,26 @@
         <v>492</v>
       </c>
       <c r="Y96" s="7" t="s">
-        <v>826</v>
+        <v>820</v>
       </c>
       <c r="Z96" s="5" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="AB96" s="5" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
     </row>
     <row r="97" spans="1:28" s="5" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A97" s="8">
+      <c r="A97" s="5">
         <v>96</v>
       </c>
-      <c r="B97" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C97" s="8" t="s">
+      <c r="B97" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C97" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="D97" s="8" t="s">
+      <c r="D97" s="5" t="s">
         <v>242</v>
       </c>
       <c r="E97" s="5" t="s">
@@ -9641,25 +9649,25 @@
         <v>444</v>
       </c>
       <c r="L97" s="5" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="M97" s="5" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="N97" s="5" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="O97" s="5" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="P97" s="5" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="R97" s="5" t="s">
         <v>477</v>
       </c>
       <c r="S97" s="5" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="V97" s="5" t="s">
         <v>466</v>
@@ -9671,26 +9679,26 @@
         <v>492</v>
       </c>
       <c r="Y97" s="7" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="Z97" s="5" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="AB97" s="5" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
     </row>
     <row r="98" spans="1:28" s="5" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A98" s="8">
+      <c r="A98" s="5">
         <v>97</v>
       </c>
-      <c r="B98" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C98" s="8" t="s">
+      <c r="B98" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C98" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="D98" s="8" t="s">
+      <c r="D98" s="5" t="s">
         <v>243</v>
       </c>
       <c r="E98" s="5" t="s">
@@ -9706,25 +9714,25 @@
         <v>444</v>
       </c>
       <c r="L98" s="5" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="M98" s="5" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="N98" s="5" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="O98" s="5" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="P98" s="5" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="R98" s="5" t="s">
         <v>477</v>
       </c>
       <c r="S98" s="5" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="V98" s="5" t="s">
         <v>466</v>
@@ -9736,26 +9744,26 @@
         <v>492</v>
       </c>
       <c r="Y98" s="7" t="s">
-        <v>828</v>
+        <v>822</v>
       </c>
       <c r="Z98" s="5" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="AB98" s="5" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
     </row>
     <row r="99" spans="1:28" s="5" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A99" s="8">
+      <c r="A99" s="5">
         <v>98</v>
       </c>
-      <c r="B99" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C99" s="8" t="s">
+      <c r="B99" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C99" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D99" s="8" t="s">
+      <c r="D99" s="5" t="s">
         <v>244</v>
       </c>
       <c r="E99" s="5" t="s">
@@ -9771,25 +9779,25 @@
         <v>444</v>
       </c>
       <c r="L99" s="5" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="M99" s="5" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="N99" s="5" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="O99" s="5" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="P99" s="5" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="R99" s="5" t="s">
         <v>477</v>
       </c>
       <c r="S99" s="5" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="V99" s="5" t="s">
         <v>466</v>
@@ -9801,26 +9809,26 @@
         <v>492</v>
       </c>
       <c r="Y99" s="7" t="s">
-        <v>829</v>
+        <v>823</v>
       </c>
       <c r="Z99" s="5" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="AB99" s="5" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
     </row>
     <row r="100" spans="1:28" s="5" customFormat="1" ht="158.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="8">
+      <c r="A100" s="5">
         <v>99</v>
       </c>
-      <c r="B100" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C100" s="8" t="s">
+      <c r="B100" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C100" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="D100" s="8" t="s">
+      <c r="D100" s="5" t="s">
         <v>245</v>
       </c>
       <c r="E100" s="5" t="s">
@@ -9836,25 +9844,25 @@
         <v>444</v>
       </c>
       <c r="L100" s="5" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="M100" s="5" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="N100" s="5" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="O100" s="5" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="P100" s="5" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="R100" s="5" t="s">
         <v>477</v>
       </c>
       <c r="S100" s="5" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="V100" s="5" t="s">
         <v>466</v>
@@ -9866,26 +9874,26 @@
         <v>492</v>
       </c>
       <c r="Y100" s="7" t="s">
-        <v>830</v>
+        <v>824</v>
       </c>
       <c r="Z100" s="5" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="AB100" s="5" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
     </row>
     <row r="101" spans="1:28" s="5" customFormat="1" ht="183.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="8">
+      <c r="A101" s="5">
         <v>100</v>
       </c>
-      <c r="B101" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C101" s="8" t="s">
+      <c r="B101" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C101" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="D101" s="8" t="s">
+      <c r="D101" s="5" t="s">
         <v>246</v>
       </c>
       <c r="E101" s="5" t="s">
@@ -9901,25 +9909,25 @@
         <v>444</v>
       </c>
       <c r="L101" s="5" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="M101" s="5" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="N101" s="5" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="O101" s="5" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="P101" s="5" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="R101" s="5" t="s">
         <v>477</v>
       </c>
       <c r="S101" s="5" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="V101" s="5" t="s">
         <v>466</v>
@@ -9931,26 +9939,26 @@
         <v>492</v>
       </c>
       <c r="Y101" s="7" t="s">
-        <v>831</v>
+        <v>825</v>
       </c>
       <c r="Z101" s="5" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="AB101" s="5" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
     </row>
     <row r="102" spans="1:28" s="5" customFormat="1" ht="159.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="8">
+      <c r="A102" s="5">
         <v>101</v>
       </c>
-      <c r="B102" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C102" s="8" t="s">
+      <c r="B102" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C102" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="D102" s="8" t="s">
+      <c r="D102" s="5" t="s">
         <v>247</v>
       </c>
       <c r="E102" s="5" t="s">
@@ -9966,25 +9974,25 @@
         <v>444</v>
       </c>
       <c r="L102" s="5" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="M102" s="5" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="N102" s="5" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="O102" s="5" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="P102" s="5" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="R102" s="5" t="s">
         <v>477</v>
       </c>
       <c r="S102" s="5" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="V102" s="5" t="s">
         <v>466</v>
@@ -9996,26 +10004,26 @@
         <v>492</v>
       </c>
       <c r="Y102" s="7" t="s">
-        <v>832</v>
+        <v>826</v>
       </c>
       <c r="Z102" s="5" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="AB102" s="5" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
     </row>
     <row r="103" spans="1:28" s="5" customFormat="1" ht="164.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="8">
+      <c r="A103" s="5">
         <v>102</v>
       </c>
-      <c r="B103" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C103" s="8" t="s">
+      <c r="B103" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C103" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D103" s="8" t="s">
+      <c r="D103" s="5" t="s">
         <v>248</v>
       </c>
       <c r="E103" s="5" t="s">
@@ -10031,25 +10039,25 @@
         <v>444</v>
       </c>
       <c r="L103" s="5" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="M103" s="5" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="N103" s="5" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="O103" s="5" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="P103" s="5" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="R103" s="5" t="s">
         <v>477</v>
       </c>
       <c r="S103" s="5" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="V103" s="5" t="s">
         <v>466</v>
@@ -10061,26 +10069,26 @@
         <v>492</v>
       </c>
       <c r="Y103" s="7" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="Z103" s="5" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="AB103" s="5" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
     </row>
     <row r="104" spans="1:28" s="5" customFormat="1" ht="164.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="8">
+      <c r="A104" s="5">
         <v>103</v>
       </c>
-      <c r="B104" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C104" s="8" t="s">
+      <c r="B104" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C104" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D104" s="8" t="s">
+      <c r="D104" s="5" t="s">
         <v>249</v>
       </c>
       <c r="E104" s="5" t="s">
@@ -10096,25 +10104,25 @@
         <v>444</v>
       </c>
       <c r="L104" s="5" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="M104" s="5" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="N104" s="5" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="O104" s="5" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="P104" s="5" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="R104" s="5" t="s">
         <v>477</v>
       </c>
       <c r="S104" s="5" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="V104" s="5" t="s">
         <v>466</v>
@@ -10126,26 +10134,26 @@
         <v>492</v>
       </c>
       <c r="Y104" s="7" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="Z104" s="5" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="AB104" s="5" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
     </row>
     <row r="105" spans="1:28" s="5" customFormat="1" ht="148.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="8">
+      <c r="A105" s="5">
         <v>104</v>
       </c>
-      <c r="B105" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C105" s="8" t="s">
+      <c r="B105" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C105" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="D105" s="8" t="s">
+      <c r="D105" s="5" t="s">
         <v>250</v>
       </c>
       <c r="E105" s="5" t="s">
@@ -10161,25 +10169,25 @@
         <v>444</v>
       </c>
       <c r="L105" s="5" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="M105" s="5" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="N105" s="5" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="O105" s="5" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="P105" s="5" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="R105" s="5" t="s">
         <v>477</v>
       </c>
       <c r="S105" s="5" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="V105" s="5" t="s">
         <v>466</v>
@@ -10191,26 +10199,26 @@
         <v>492</v>
       </c>
       <c r="Y105" s="7" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="Z105" s="5" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="AB105" s="5" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
     </row>
     <row r="106" spans="1:28" s="5" customFormat="1" ht="101.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="8">
+      <c r="A106" s="5">
         <v>105</v>
       </c>
-      <c r="B106" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C106" s="8" t="s">
+      <c r="B106" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C106" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="D106" s="8" t="s">
+      <c r="D106" s="5" t="s">
         <v>251</v>
       </c>
       <c r="E106" s="5" t="s">
@@ -10226,25 +10234,25 @@
         <v>444</v>
       </c>
       <c r="L106" s="5" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="M106" s="5" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="N106" s="5" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="O106" s="5" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="P106" s="5" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="R106" s="5" t="s">
         <v>477</v>
       </c>
       <c r="S106" s="5" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="V106" s="5" t="s">
         <v>466</v>
@@ -10256,26 +10264,26 @@
         <v>492</v>
       </c>
       <c r="Y106" s="7" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="Z106" s="5" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="AB106" s="5" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
     </row>
     <row r="107" spans="1:28" s="5" customFormat="1" ht="132" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="8">
+      <c r="A107" s="5">
         <v>106</v>
       </c>
-      <c r="B107" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C107" s="8" t="s">
+      <c r="B107" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C107" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="D107" s="8" t="s">
+      <c r="D107" s="5" t="s">
         <v>252</v>
       </c>
       <c r="E107" s="5" t="s">
@@ -10291,25 +10299,25 @@
         <v>444</v>
       </c>
       <c r="L107" s="5" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="M107" s="5" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="N107" s="5" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="O107" s="5" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="P107" s="5" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="R107" s="5" t="s">
         <v>477</v>
       </c>
       <c r="S107" s="5" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="V107" s="5" t="s">
         <v>466</v>
@@ -10321,26 +10329,26 @@
         <v>492</v>
       </c>
       <c r="Y107" s="7" t="s">
-        <v>837</v>
+        <v>831</v>
       </c>
       <c r="Z107" s="5" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="AB107" s="5" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
     </row>
     <row r="108" spans="1:28" s="5" customFormat="1" ht="148.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="8">
+      <c r="A108" s="5">
         <v>107</v>
       </c>
-      <c r="B108" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C108" s="8" t="s">
+      <c r="B108" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C108" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="D108" s="8" t="s">
+      <c r="D108" s="5" t="s">
         <v>253</v>
       </c>
       <c r="E108" s="5" t="s">
@@ -10356,25 +10364,25 @@
         <v>444</v>
       </c>
       <c r="L108" s="5" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="M108" s="5" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="N108" s="5" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="O108" s="5" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="P108" s="5" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="R108" s="5" t="s">
         <v>477</v>
       </c>
       <c r="S108" s="5" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="V108" s="5" t="s">
         <v>466</v>
@@ -10386,26 +10394,26 @@
         <v>492</v>
       </c>
       <c r="Y108" s="7" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="Z108" s="5" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="AB108" s="5" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
     </row>
     <row r="109" spans="1:28" s="5" customFormat="1" ht="176.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="8">
+      <c r="A109" s="5">
         <v>108</v>
       </c>
-      <c r="B109" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C109" s="8" t="s">
+      <c r="B109" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C109" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="D109" s="8" t="s">
+      <c r="D109" s="5" t="s">
         <v>254</v>
       </c>
       <c r="E109" s="5" t="s">
@@ -10421,25 +10429,25 @@
         <v>444</v>
       </c>
       <c r="L109" s="5" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="M109" s="5" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="N109" s="5" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="O109" s="5" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="P109" s="5" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="R109" s="5" t="s">
         <v>477</v>
       </c>
       <c r="S109" s="5" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="V109" s="5" t="s">
         <v>466</v>
@@ -10451,26 +10459,26 @@
         <v>492</v>
       </c>
       <c r="Y109" s="7" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="Z109" s="5" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="AB109" s="5" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
     </row>
     <row r="110" spans="1:28" s="5" customFormat="1" ht="255" x14ac:dyDescent="0.25">
-      <c r="A110" s="8">
+      <c r="A110" s="5">
         <v>109</v>
       </c>
-      <c r="B110" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C110" s="8" t="s">
+      <c r="B110" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C110" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="D110" s="8" t="s">
+      <c r="D110" s="5" t="s">
         <v>255</v>
       </c>
       <c r="E110" s="5" t="s">
@@ -10486,16 +10494,16 @@
         <v>444</v>
       </c>
       <c r="L110" s="5" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="M110" s="5" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="N110" s="5" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="O110" s="5" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="P110" s="5" t="s">
         <v>524</v>
@@ -10504,7 +10512,7 @@
         <v>477</v>
       </c>
       <c r="S110" s="5" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="V110" s="5" t="s">
         <v>466</v>
@@ -10516,20 +10524,20 @@
         <v>479</v>
       </c>
       <c r="Y110" s="5" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
     </row>
     <row r="111" spans="1:28" s="5" customFormat="1" ht="255" x14ac:dyDescent="0.25">
-      <c r="A111" s="8">
+      <c r="A111" s="5">
         <v>110</v>
       </c>
-      <c r="B111" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C111" s="8" t="s">
+      <c r="B111" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C111" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="D111" s="8" t="s">
+      <c r="D111" s="5" t="s">
         <v>256</v>
       </c>
       <c r="E111" s="5" t="s">
@@ -10561,16 +10569,16 @@
       </c>
     </row>
     <row r="112" spans="1:28" s="5" customFormat="1" ht="255" x14ac:dyDescent="0.25">
-      <c r="A112" s="8">
+      <c r="A112" s="5">
         <v>111</v>
       </c>
-      <c r="B112" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C112" s="8" t="s">
+      <c r="B112" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C112" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="D112" s="8" t="s">
+      <c r="D112" s="5" t="s">
         <v>257</v>
       </c>
       <c r="E112" s="5" t="s">
@@ -10602,16 +10610,16 @@
       </c>
     </row>
     <row r="113" spans="1:28" s="5" customFormat="1" ht="255" x14ac:dyDescent="0.25">
-      <c r="A113" s="8">
+      <c r="A113" s="5">
         <v>112</v>
       </c>
-      <c r="B113" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C113" s="8" t="s">
+      <c r="B113" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C113" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="D113" s="8" t="s">
+      <c r="D113" s="5" t="s">
         <v>258</v>
       </c>
       <c r="E113" s="5" t="s">
@@ -10627,22 +10635,22 @@
         <v>444</v>
       </c>
       <c r="L113" s="7" t="s">
-        <v>889</v>
+        <v>881</v>
       </c>
       <c r="M113" s="7" t="s">
-        <v>890</v>
+        <v>882</v>
       </c>
       <c r="N113" s="5" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="O113" s="5" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="S113" s="5" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="U113" s="7" t="s">
-        <v>882</v>
+        <v>874</v>
       </c>
       <c r="V113" s="5" t="s">
         <v>466</v>
@@ -10654,26 +10662,26 @@
         <v>492</v>
       </c>
       <c r="Y113" s="7" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="Z113" s="5" t="s">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="AB113" s="5" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
     </row>
     <row r="114" spans="1:28" s="5" customFormat="1" ht="255" x14ac:dyDescent="0.25">
-      <c r="A114" s="8">
+      <c r="A114" s="5">
         <v>113</v>
       </c>
-      <c r="B114" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C114" s="8" t="s">
+      <c r="B114" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C114" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="D114" s="8" t="s">
+      <c r="D114" s="5" t="s">
         <v>259</v>
       </c>
       <c r="E114" s="5" t="s">
@@ -10689,28 +10697,28 @@
         <v>444</v>
       </c>
       <c r="L114" s="5" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="M114" s="5" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="N114" s="5" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="O114" s="5" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="P114" s="5" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="R114" s="5" t="s">
         <v>477</v>
       </c>
       <c r="S114" s="5" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="U114" s="7" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="V114" s="5" t="s">
         <v>466</v>
@@ -10722,23 +10730,23 @@
         <v>492</v>
       </c>
       <c r="Y114" s="5" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="Z114" s="5" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
     </row>
     <row r="115" spans="1:28" s="5" customFormat="1" ht="255" x14ac:dyDescent="0.25">
-      <c r="A115" s="8">
+      <c r="A115" s="5">
         <v>114</v>
       </c>
-      <c r="B115" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C115" s="8" t="s">
+      <c r="B115" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C115" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="D115" s="8" t="s">
+      <c r="D115" s="5" t="s">
         <v>260</v>
       </c>
       <c r="E115" s="5" t="s">
@@ -10754,25 +10762,25 @@
         <v>444</v>
       </c>
       <c r="L115" s="5" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="M115" s="5" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="N115" s="5" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="O115" s="5" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="P115" s="5" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="R115" s="5" t="s">
         <v>477</v>
       </c>
       <c r="S115" s="5" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="V115" s="5" t="s">
         <v>466</v>
@@ -10784,23 +10792,23 @@
         <v>492</v>
       </c>
       <c r="Y115" s="5" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="Z115" s="5" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
     </row>
     <row r="116" spans="1:28" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A116" s="8">
+      <c r="A116" s="5">
         <v>115</v>
       </c>
-      <c r="B116" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C116" s="8" t="s">
+      <c r="B116" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C116" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="D116" s="8" t="s">
+      <c r="D116" s="5" t="s">
         <v>261</v>
       </c>
       <c r="E116" s="5" t="s">
@@ -10829,16 +10837,16 @@
       </c>
     </row>
     <row r="117" spans="1:28" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A117" s="8">
+      <c r="A117" s="5">
         <v>116</v>
       </c>
-      <c r="B117" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C117" s="8" t="s">
+      <c r="B117" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C117" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="D117" s="8" t="s">
+      <c r="D117" s="5" t="s">
         <v>262</v>
       </c>
       <c r="E117" s="5" t="s">
@@ -10867,16 +10875,16 @@
       </c>
     </row>
     <row r="118" spans="1:28" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A118" s="8">
+      <c r="A118" s="5">
         <v>117</v>
       </c>
-      <c r="B118" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C118" s="8" t="s">
+      <c r="B118" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C118" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="D118" s="8" t="s">
+      <c r="D118" s="5" t="s">
         <v>263</v>
       </c>
       <c r="E118" s="5" t="s">
@@ -10905,16 +10913,16 @@
       </c>
     </row>
     <row r="119" spans="1:28" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A119" s="8">
+      <c r="A119" s="5">
         <v>118</v>
       </c>
-      <c r="B119" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C119" s="8" t="s">
+      <c r="B119" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C119" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D119" s="8" t="s">
+      <c r="D119" s="5" t="s">
         <v>264</v>
       </c>
       <c r="E119" s="5" t="s">
@@ -10943,16 +10951,16 @@
       </c>
     </row>
     <row r="120" spans="1:28" s="5" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A120" s="8">
+      <c r="A120" s="5">
         <v>119</v>
       </c>
-      <c r="B120" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C120" s="8" t="s">
+      <c r="B120" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C120" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="D120" s="8" t="s">
+      <c r="D120" s="5" t="s">
         <v>265</v>
       </c>
       <c r="E120" s="5" t="s">
@@ -10965,22 +10973,22 @@
         <v>407</v>
       </c>
       <c r="L120" s="5" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="M120" s="5" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="N120" s="5" t="s">
-        <v>805</v>
+        <v>799</v>
       </c>
       <c r="O120" s="5" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="P120" s="5" t="s">
         <v>564</v>
       </c>
       <c r="S120" s="5" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="V120" s="5" t="s">
         <v>466</v>
@@ -10992,23 +11000,23 @@
         <v>492</v>
       </c>
       <c r="Y120" s="5" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="Z120" s="5" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
     </row>
     <row r="121" spans="1:28" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A121" s="8">
+      <c r="A121" s="5">
         <v>120</v>
       </c>
-      <c r="B121" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C121" s="8" t="s">
+      <c r="B121" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C121" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="D121" s="8" t="s">
+      <c r="D121" s="5" t="s">
         <v>266</v>
       </c>
       <c r="E121" s="5" t="s">
@@ -11037,16 +11045,16 @@
       </c>
     </row>
     <row r="122" spans="1:28" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A122" s="8">
+      <c r="A122" s="5">
         <v>121</v>
       </c>
-      <c r="B122" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="C122" s="8" t="s">
+      <c r="B122" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C122" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="D122" s="8" t="s">
+      <c r="D122" s="5" t="s">
         <v>267</v>
       </c>
       <c r="E122" s="5" t="s">
